--- a/DOCX/Net3_Group_14 (3).xlsx
+++ b/DOCX/Net3_Group_14 (3).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8000"/>
+    <workbookView windowWidth="19200" windowHeight="7550"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -92,7 +92,7 @@
     <t>056206010544</t>
   </si>
   <si>
-    <t>code MainWindow.cpp (Server), main (Server) + testcase</t>
+    <t>code MainWindow.cpp (Server), main (Server)</t>
   </si>
   <si>
     <t>https://github.com/canh0502</t>
@@ -120,7 +120,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,13 +146,6 @@
       <color rgb="FF202020"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -617,161 +610,157 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -791,9 +780,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1142,11 +1128,11 @@
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="1"/>
+      <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8">
       <c r="B3" s="1" t="s">
@@ -1155,131 +1141,131 @@
       <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1"/>
+      <c r="H3" s="1"/>
     </row>
     <row r="4" spans="2:8">
       <c r="B4" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
     </row>
     <row r="5" spans="2:8">
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="B5" s="1"/>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
     </row>
     <row r="6" spans="2:8">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" ht="62" customHeight="1" spans="2:8">
-      <c r="B7" s="6">
+      <c r="B7" s="4">
         <v>1</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="4">
         <v>56307008420</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="8" ht="54" spans="2:8">
-      <c r="B8" s="11">
+      <c r="B8" s="9">
         <v>2</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="16" t="s">
+      <c r="D8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" ht="40.5" spans="2:8">
-      <c r="B9" s="11">
+    <row r="9" ht="27" spans="2:8">
+      <c r="B9" s="9">
         <v>3</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="D9" s="16" t="s">
+      <c r="D9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>1</v>
       </c>
     </row>
     <row r="10" ht="40.5" spans="2:8">
-      <c r="B10" s="11">
+      <c r="B10" s="9">
         <v>4</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="10">
+      <c r="G10" s="8">
         <v>1</v>
       </c>
     </row>
